--- a/research/traditional_assets/database/data/nigeria/nigeria_advertising.xlsx
+++ b/research/traditional_assets/database/data/nigeria/nigeria_advertising.xlsx
@@ -587,8 +587,23 @@
           <t>Advertising</t>
         </is>
       </c>
+      <c r="G2">
+        <v>1.190721649484536</v>
+      </c>
+      <c r="H2">
+        <v>0.8118556701030928</v>
+      </c>
+      <c r="I2">
+        <v>0.6146907216494845</v>
+      </c>
+      <c r="J2">
+        <v>0.5195451109664685</v>
+      </c>
       <c r="K2">
-        <v>0</v>
+        <v>0.415</v>
+      </c>
+      <c r="L2">
+        <v>0.5347938144329897</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -596,71 +611,74 @@
       <c r="N2">
         <v>0</v>
       </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
       <c r="P2">
         <v>0</v>
       </c>
       <c r="Q2">
         <v>0</v>
       </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.005</v>
+        <v>0.008</v>
       </c>
       <c r="V2">
-        <v>0.002325581395348837</v>
+        <v>0.00404040404040404</v>
       </c>
       <c r="W2">
-        <v>-0</v>
+        <v>-0.051875</v>
       </c>
       <c r="X2">
-        <v>0.1314728412601764</v>
+        <v>0.2490753624106469</v>
       </c>
       <c r="Y2">
-        <v>-0.1314728412601764</v>
-      </c>
-      <c r="Z2">
-        <v>-0</v>
-      </c>
-      <c r="AA2">
-        <v>-0</v>
+        <v>-0.3009503624106469</v>
       </c>
       <c r="AB2">
-        <v>0.1273387874767915</v>
-      </c>
-      <c r="AC2">
-        <v>-0.1273387874767915</v>
+        <v>0.2406494488648794</v>
       </c>
       <c r="AD2">
-        <v>0.122</v>
+        <v>0.116</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.122</v>
+        <v>0.116</v>
       </c>
       <c r="AG2">
-        <v>0.117</v>
+        <v>0.108</v>
       </c>
       <c r="AH2">
-        <v>0.05369718309859155</v>
+        <v>0.05534351145038168</v>
       </c>
       <c r="AI2">
-        <v>-0.01548616400101548</v>
+        <v>-0.01543784934788395</v>
       </c>
       <c r="AJ2">
-        <v>0.05161005734450816</v>
+        <v>0.05172413793103449</v>
       </c>
       <c r="AK2">
-        <v>-0.01484206520360269</v>
+        <v>-0.01435788354161128</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
         <v>0</v>
+      </c>
+      <c r="AN2">
+        <v>0.1617852161785216</v>
+      </c>
+      <c r="AP2">
+        <v>0.1506276150627615</v>
       </c>
     </row>
     <row r="3">
@@ -679,8 +697,23 @@
           <t>Advertising</t>
         </is>
       </c>
+      <c r="G3">
+        <v>1.190721649484536</v>
+      </c>
+      <c r="H3">
+        <v>0.8118556701030928</v>
+      </c>
+      <c r="I3">
+        <v>0.6146907216494845</v>
+      </c>
+      <c r="J3">
+        <v>0.5195451109664685</v>
+      </c>
       <c r="K3">
-        <v>0</v>
+        <v>0.415</v>
+      </c>
+      <c r="L3">
+        <v>0.5347938144329897</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -688,71 +721,74 @@
       <c r="N3">
         <v>-0</v>
       </c>
+      <c r="O3">
+        <v>-0</v>
+      </c>
       <c r="P3">
         <v>-0</v>
       </c>
       <c r="Q3">
         <v>-0</v>
       </c>
+      <c r="R3">
+        <v>-0</v>
+      </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.005</v>
+        <v>0.008</v>
       </c>
       <c r="V3">
-        <v>0.002325581395348837</v>
+        <v>0.00404040404040404</v>
       </c>
       <c r="W3">
-        <v>-0</v>
+        <v>-0.051875</v>
       </c>
       <c r="X3">
-        <v>0.1314728412601764</v>
+        <v>0.2490753624106469</v>
       </c>
       <c r="Y3">
-        <v>-0.1314728412601764</v>
-      </c>
-      <c r="Z3">
-        <v>-0</v>
-      </c>
-      <c r="AA3">
-        <v>-0</v>
+        <v>-0.3009503624106469</v>
       </c>
       <c r="AB3">
-        <v>0.1273387874767915</v>
-      </c>
-      <c r="AC3">
-        <v>-0.1273387874767915</v>
+        <v>0.2406494488648794</v>
       </c>
       <c r="AD3">
-        <v>0.122</v>
+        <v>0.116</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.122</v>
+        <v>0.116</v>
       </c>
       <c r="AG3">
-        <v>0.117</v>
+        <v>0.108</v>
       </c>
       <c r="AH3">
-        <v>0.05369718309859155</v>
+        <v>0.05534351145038168</v>
       </c>
       <c r="AI3">
-        <v>-0.01548616400101548</v>
+        <v>-0.01543784934788395</v>
       </c>
       <c r="AJ3">
-        <v>0.05161005734450816</v>
+        <v>0.05172413793103449</v>
       </c>
       <c r="AK3">
-        <v>-0.01484206520360269</v>
+        <v>-0.01435788354161128</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
         <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>0.1617852161785216</v>
+      </c>
+      <c r="AP3">
+        <v>0.1506276150627615</v>
       </c>
     </row>
   </sheetData>
